--- a/RS_D620/documents/RS_620_scratchpad.xlsx
+++ b/RS_D620/documents/RS_620_scratchpad.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\POC\RS_D620\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7399D1-610A-42E9-9A06-E6397FB3040A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058E56C5-8868-47D2-9F11-BCE8CD9E68B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21495" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{77793D01-6217-42E2-9AFC-8B7FA38831D5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77793D01-6217-42E2-9AFC-8B7FA38831D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="163">
   <si>
     <t>MON1</t>
   </si>
@@ -74,18 +77,12 @@
     <t>…</t>
   </si>
   <si>
-    <t>DMON8</t>
-  </si>
-  <si>
     <t>MON24</t>
   </si>
   <si>
     <t>EN1</t>
   </si>
   <si>
-    <t>EN32</t>
-  </si>
-  <si>
     <t>MAR1'</t>
   </si>
   <si>
@@ -110,7 +107,430 @@
     <t>PMBUS_ADDR2</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>EK-RA6M5</t>
+  </si>
+  <si>
+    <t>controler config</t>
+  </si>
+  <si>
+    <t>fault_mapping</t>
+  </si>
+  <si>
+    <t>map addr</t>
+  </si>
+  <si>
+    <t>flash</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>MON10</t>
+  </si>
+  <si>
+    <t>MON11</t>
+  </si>
+  <si>
+    <t>MON12</t>
+  </si>
+  <si>
+    <t>MON13</t>
+  </si>
+  <si>
+    <t>MON14</t>
+  </si>
+  <si>
+    <t>MON15</t>
+  </si>
+  <si>
+    <t>MON16</t>
+  </si>
+  <si>
+    <t>MON17</t>
+  </si>
+  <si>
+    <t>MON18</t>
+  </si>
+  <si>
+    <t>MON19</t>
+  </si>
+  <si>
+    <t>MON20</t>
+  </si>
+  <si>
+    <t>MON21</t>
+  </si>
+  <si>
+    <t>MON22</t>
+  </si>
+  <si>
+    <t>MON23</t>
+  </si>
+  <si>
+    <t>analog only</t>
+  </si>
+  <si>
+    <t>P000</t>
+  </si>
+  <si>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>SW2</t>
+  </si>
+  <si>
+    <t>SW1</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>BLUE LED</t>
+  </si>
+  <si>
+    <t>GREEN LED</t>
+  </si>
+  <si>
+    <t>RED LED</t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>AN003</t>
+  </si>
+  <si>
+    <t>AN000/AN100</t>
+  </si>
+  <si>
+    <t>AN001/AN101</t>
+  </si>
+  <si>
+    <t>AN002/AN102</t>
+  </si>
+  <si>
+    <t>AN004</t>
+  </si>
+  <si>
+    <t>AN005</t>
+  </si>
+  <si>
+    <t>AN006</t>
+  </si>
+  <si>
+    <t>AN007</t>
+  </si>
+  <si>
+    <t>AN008</t>
+  </si>
+  <si>
+    <t>AN009</t>
+  </si>
+  <si>
+    <t>AN010</t>
+  </si>
+  <si>
+    <t>P014</t>
+  </si>
+  <si>
+    <t>AN012</t>
+  </si>
+  <si>
+    <t>P015</t>
+  </si>
+  <si>
+    <t>AN013</t>
+  </si>
+  <si>
+    <t>P500</t>
+  </si>
+  <si>
+    <t>P501</t>
+  </si>
+  <si>
+    <t>P502</t>
+  </si>
+  <si>
+    <t>P503</t>
+  </si>
+  <si>
+    <t>P504</t>
+  </si>
+  <si>
+    <t>P505</t>
+  </si>
+  <si>
+    <t>P506</t>
+  </si>
+  <si>
+    <t>P507</t>
+  </si>
+  <si>
+    <t>P508</t>
+  </si>
+  <si>
+    <t>P800</t>
+  </si>
+  <si>
+    <t>P801</t>
+  </si>
+  <si>
+    <t>P802</t>
+  </si>
+  <si>
+    <t>AN116</t>
+  </si>
+  <si>
+    <t>AN117</t>
+  </si>
+  <si>
+    <t>AN118</t>
+  </si>
+  <si>
+    <t>AN119</t>
+  </si>
+  <si>
+    <t>AN120</t>
+  </si>
+  <si>
+    <t>AN121</t>
+  </si>
+  <si>
+    <t>AN122</t>
+  </si>
+  <si>
+    <t>AN123</t>
+  </si>
+  <si>
+    <t>AN124</t>
+  </si>
+  <si>
+    <t>AN125</t>
+  </si>
+  <si>
+    <t>AN126</t>
+  </si>
+  <si>
+    <t>P803</t>
+  </si>
+  <si>
+    <t>AN127</t>
+  </si>
+  <si>
+    <t>AN128</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>1k5 pullup</t>
+  </si>
+  <si>
+    <t>1k5 pulluo</t>
+  </si>
+  <si>
+    <t>P105</t>
+  </si>
+  <si>
+    <t>P206</t>
+  </si>
+  <si>
+    <t>P400</t>
+  </si>
+  <si>
+    <t>P806</t>
+  </si>
+  <si>
+    <t>IRQ0</t>
+  </si>
+  <si>
+    <t>IRQ1</t>
+  </si>
+  <si>
+    <t>P101</t>
+  </si>
+  <si>
+    <t>P104</t>
+  </si>
+  <si>
+    <t>P205</t>
+  </si>
+  <si>
+    <t>P804</t>
+  </si>
+  <si>
+    <t>IRQ2</t>
+  </si>
+  <si>
+    <t>P100</t>
+  </si>
+  <si>
+    <t>P203</t>
+  </si>
+  <si>
+    <t>P213</t>
+  </si>
+  <si>
+    <t>P110</t>
+  </si>
+  <si>
+    <t>P202</t>
+  </si>
+  <si>
+    <t>P212</t>
+  </si>
+  <si>
+    <t>P111</t>
+  </si>
+  <si>
+    <t>IRQ3</t>
+  </si>
+  <si>
+    <t>IRQ4</t>
+  </si>
+  <si>
+    <t>P402</t>
+  </si>
+  <si>
+    <t>P411</t>
+  </si>
+  <si>
+    <t>PA10</t>
+  </si>
+  <si>
+    <t>IRQ5</t>
+  </si>
+  <si>
+    <t>P302</t>
+  </si>
+  <si>
+    <t>P401</t>
+  </si>
+  <si>
+    <t>P410</t>
+  </si>
+  <si>
+    <t>PA09</t>
+  </si>
+  <si>
+    <t>IRQ6</t>
+  </si>
+  <si>
+    <t>P301</t>
+  </si>
+  <si>
+    <t>P409 (2)</t>
+  </si>
+  <si>
+    <t>PA08</t>
+  </si>
+  <si>
+    <t>IRQ7</t>
+  </si>
+  <si>
+    <t>P408</t>
+  </si>
+  <si>
+    <t>P615</t>
+  </si>
+  <si>
+    <t>P706</t>
+  </si>
+  <si>
+    <t>IRQ8</t>
+  </si>
+  <si>
+    <t>P305 (6)</t>
+  </si>
+  <si>
+    <t>P415 (7)</t>
+  </si>
+  <si>
+    <t>&lt;-- 1k5 pu</t>
+  </si>
+  <si>
+    <t>P707</t>
+  </si>
+  <si>
+    <t>force low</t>
+  </si>
+  <si>
+    <t>P905</t>
+  </si>
+  <si>
+    <t>IRQ9</t>
+  </si>
+  <si>
+    <t>P304</t>
+  </si>
+  <si>
+    <t>P414</t>
+  </si>
+  <si>
+    <t>IRQ10</t>
+  </si>
+  <si>
+    <t>IRQ11</t>
+  </si>
+  <si>
+    <t>IRQ14</t>
+  </si>
+  <si>
+    <t>IRQ15</t>
+  </si>
+  <si>
+    <t>P906</t>
+  </si>
+  <si>
+    <t>P907</t>
+  </si>
+  <si>
+    <t>P908</t>
+  </si>
+  <si>
+    <t>P708</t>
+  </si>
+  <si>
+    <t>P403</t>
+  </si>
+  <si>
+    <t>P512</t>
+  </si>
+  <si>
+    <t>SCL</t>
+  </si>
+  <si>
+    <t>P404</t>
+  </si>
+  <si>
+    <t>P511</t>
+  </si>
+  <si>
+    <t>SDA</t>
+  </si>
+  <si>
+    <t>Interrupt table pin map</t>
   </si>
 </sst>
 </file>
@@ -126,12 +546,54 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -146,16 +608,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF7C80"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -484,148 +965,2571 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2196B8D-FE2F-4541-9D73-52590DEE3D06}">
-  <dimension ref="B3:B34"/>
+  <dimension ref="A2:K90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D29" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C31" t="str">
+        <f>_xlfn.CONCAT("DMON",RIGHT(C30,1)+1)</f>
+        <v>DMON2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>107</v>
+      </c>
+      <c r="F31" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C32" t="str">
+        <f t="shared" ref="C32:C36" si="0">_xlfn.CONCAT("DMON",RIGHT(C31,1)+1)</f>
+        <v>DMON3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32" t="s">
+        <v>113</v>
+      </c>
+      <c r="G32" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>DMON4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>DMON5</v>
+      </c>
+      <c r="E34" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" t="s">
+        <v>123</v>
+      </c>
+      <c r="I34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>DMON6</v>
+      </c>
+      <c r="E35" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" t="s">
+        <v>127</v>
+      </c>
+      <c r="H35" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>DMON7</v>
+      </c>
+      <c r="E36" t="s">
+        <v>130</v>
+      </c>
+      <c r="F36" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="I36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>138</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I38" t="s">
+        <v>144</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>148</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="I40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" t="s">
+        <v>155</v>
+      </c>
+      <c r="I41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" t="s">
+        <v>150</v>
+      </c>
+      <c r="G42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E43" t="s">
+        <v>151</v>
+      </c>
+      <c r="G43" t="s">
+        <v>159</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C46" t="str">
+        <f>_xlfn.CONCAT("EN",RIGHT(C45,1)+1)</f>
+        <v>EN2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C47" t="str">
+        <f t="shared" ref="C47:C54" si="1">_xlfn.CONCAT("EN",RIGHT(C46,1)+1)</f>
+        <v>EN3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C48" t="str">
+        <f t="shared" si="1"/>
+        <v>EN4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" t="str">
+        <f t="shared" si="1"/>
+        <v>EN5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50" t="str">
+        <f t="shared" si="1"/>
+        <v>EN6</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51" t="str">
+        <f t="shared" si="1"/>
+        <v>EN7</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C52" t="str">
+        <f t="shared" si="1"/>
+        <v>EN8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C53" t="str">
+        <f t="shared" si="1"/>
+        <v>EN9</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C54" t="str">
+        <f t="shared" si="1"/>
+        <v>EN10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C55" t="str">
+        <f>_xlfn.CONCAT("EN",RIGHT(C54,2)+1)</f>
+        <v>EN11</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C56" t="str">
+        <f t="shared" ref="C56:C75" si="2">_xlfn.CONCAT("EN",RIGHT(C55,2)+1)</f>
+        <v>EN12</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C57" t="str">
+        <f t="shared" si="2"/>
+        <v>EN13</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C58" t="str">
+        <f t="shared" si="2"/>
+        <v>EN14</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C59" t="str">
+        <f t="shared" si="2"/>
+        <v>EN15</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C60" t="str">
+        <f t="shared" si="2"/>
+        <v>EN16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C61" t="str">
+        <f t="shared" si="2"/>
+        <v>EN17</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C62" t="str">
+        <f t="shared" si="2"/>
+        <v>EN18</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C63" t="str">
+        <f t="shared" si="2"/>
+        <v>EN19</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C64" t="str">
+        <f t="shared" si="2"/>
+        <v>EN20</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C65" t="str">
+        <f t="shared" si="2"/>
+        <v>EN21</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C66" t="str">
+        <f t="shared" si="2"/>
+        <v>EN22</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C67" t="str">
+        <f t="shared" si="2"/>
+        <v>EN23</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C68" t="str">
+        <f t="shared" si="2"/>
+        <v>EN24</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C69" t="str">
+        <f t="shared" si="2"/>
+        <v>EN25</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C70" t="str">
+        <f t="shared" si="2"/>
+        <v>EN26</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C71" t="str">
+        <f t="shared" si="2"/>
+        <v>EN27</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C72" t="str">
+        <f t="shared" si="2"/>
+        <v>EN28</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C73" t="str">
+        <f t="shared" si="2"/>
+        <v>EN29</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C74" t="str">
+        <f t="shared" si="2"/>
+        <v>EN30</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C75" t="str">
+        <f t="shared" si="2"/>
+        <v>EN31</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C86" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C88" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C90" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D29:J29"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF098AE8-DFFF-4238-AAA6-7A00A365BB2F}">
+  <dimension ref="A1:J134"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <f>_xlfn.CONCAT("0x",DEC2HEX(C5,8))</f>
+        <v>0x00000000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5">
+        <v>536871968</v>
+      </c>
+      <c r="J5" t="str">
+        <f>_xlfn.CONCAT("0x",DEC2HEX(I5,8))</f>
+        <v>0x20000420</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <f t="shared" ref="C6:C39" si="0">C5+64</f>
+        <v>64</v>
+      </c>
+      <c r="D6" t="str">
+        <f>_xlfn.CONCAT("0x",DEC2HEX(C6,8))</f>
+        <v>0x00000040</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <f>64*32</f>
+        <v>2048</v>
+      </c>
+      <c r="I6">
+        <v>153</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" ref="J6:J18" si="1">_xlfn.CONCAT("0x",DEC2HEX(I6,8))</f>
+        <v>0x00000099</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="D7" t="str">
+        <f>_xlfn.CONCAT("0x",DEC2HEX(C7,8))</f>
+        <v>0x00000080</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>1113</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000459</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>192</v>
+      </c>
+      <c r="D8" t="str">
+        <f>_xlfn.CONCAT("0x",DEC2HEX(C8,8))</f>
+        <v>0x000000C0</v>
+      </c>
+      <c r="E8" t="str">
+        <f>_xlfn.CONCAT("rail[",B8,"]")</f>
+        <v>rail[0]</v>
+      </c>
+      <c r="I8">
+        <v>163</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="1"/>
+        <v>0x000000A3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <f>B8+1</f>
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>256</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" ref="D9:D72" si="2">_xlfn.CONCAT("0x",DEC2HEX(C9,8))</f>
+        <v>0x00000100</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" ref="E9:E39" si="3">_xlfn.CONCAT("rail[",B9,"]")</f>
+        <v>rail[1]</v>
+      </c>
+      <c r="I9">
+        <v>16777216</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="1"/>
+        <v>0x01000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f t="shared" ref="B10:B39" si="4">B9+1</f>
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000140</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[2]</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>384</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000180</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[3]</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>448</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000001C0</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[4]</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>512</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000200</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[5]</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>576</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000240</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[6]</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000280</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[7]</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>704</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000002C0</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[8]</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>768</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000300</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[9]</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>832</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000340</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[10]</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="1"/>
+        <v>0x00000000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>896</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000380</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[11]</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000003C0</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[12]</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>1024</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000400</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[13]</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>1088</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000440</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[14]</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>1152</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000480</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[15]</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>1216</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000004C0</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[16]</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>1280</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000500</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[17]</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>1344</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000540</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[18]</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>1408</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000580</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[19]</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>1472</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000005C0</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[20]</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>1536</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000600</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[21]</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000640</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[22]</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <f t="shared" si="4"/>
         <v>23</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>1664</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000680</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[23]</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>1728</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000006C0</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[24]</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>1792</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000700</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[25]</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>1856</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000740</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[26]</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>1920</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000780</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[27]</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <f t="shared" si="4"/>
+        <v>28</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>1984</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000007C0</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[28]</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>2048</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000800</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[29]</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>2112</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000840</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[30]</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>2176</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000880</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="3"/>
+        <v>rail[31]</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <f t="shared" ref="C40:C103" si="5">C39+64</f>
+        <v>2240</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000008C0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <f t="shared" si="5"/>
+        <v>2304</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000900</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <f t="shared" si="5"/>
+        <v>2368</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000940</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <f t="shared" si="5"/>
+        <v>2432</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000980</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <f t="shared" si="5"/>
+        <v>2496</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000009C0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C45">
+        <f t="shared" si="5"/>
+        <v>2560</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000A00</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <f t="shared" si="5"/>
+        <v>2624</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000A40</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C47">
+        <f t="shared" si="5"/>
+        <v>2688</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000A80</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C48">
+        <f t="shared" si="5"/>
+        <v>2752</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000AC0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C49">
+        <f t="shared" si="5"/>
+        <v>2816</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000B00</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C50">
+        <f t="shared" si="5"/>
+        <v>2880</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000B40</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C51">
+        <f t="shared" si="5"/>
+        <v>2944</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000B80</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <f t="shared" si="5"/>
+        <v>3008</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000BC0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C53">
+        <f t="shared" si="5"/>
+        <v>3072</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000C00</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <f t="shared" si="5"/>
+        <v>3136</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000C40</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C55">
+        <f t="shared" si="5"/>
+        <v>3200</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000C80</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C56">
+        <f t="shared" si="5"/>
+        <v>3264</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000CC0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C57">
+        <f t="shared" si="5"/>
+        <v>3328</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000D00</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C58">
+        <f t="shared" si="5"/>
+        <v>3392</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000D40</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C59">
+        <f t="shared" si="5"/>
+        <v>3456</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000D80</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <f t="shared" si="5"/>
+        <v>3520</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000DC0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C61">
+        <f t="shared" si="5"/>
+        <v>3584</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000E00</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C62">
+        <f t="shared" si="5"/>
+        <v>3648</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000E40</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C63">
+        <f t="shared" si="5"/>
+        <v>3712</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000E80</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C64">
+        <f t="shared" si="5"/>
+        <v>3776</v>
+      </c>
+      <c r="D64" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000EC0</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C65">
+        <f t="shared" si="5"/>
+        <v>3840</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000F00</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C66">
+        <f t="shared" si="5"/>
+        <v>3904</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000F40</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C67">
+        <f t="shared" si="5"/>
+        <v>3968</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000F80</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C68">
+        <f t="shared" si="5"/>
+        <v>4032</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00000FC0</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C69">
+        <f t="shared" si="5"/>
+        <v>4096</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00001000</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C70">
+        <f t="shared" si="5"/>
+        <v>4160</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00001040</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C71">
+        <f t="shared" si="5"/>
+        <v>4224</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="2"/>
+        <v>0x00001080</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C72">
+        <f t="shared" si="5"/>
+        <v>4288</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="2"/>
+        <v>0x000010C0</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C73">
+        <f t="shared" si="5"/>
+        <v>4352</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" ref="D73:D136" si="6">_xlfn.CONCAT("0x",DEC2HEX(C73,8))</f>
+        <v>0x00001100</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C74">
+        <f t="shared" si="5"/>
+        <v>4416</v>
+      </c>
+      <c r="D74" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001140</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C75">
+        <f t="shared" si="5"/>
+        <v>4480</v>
+      </c>
+      <c r="D75" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001180</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C76">
+        <f t="shared" si="5"/>
+        <v>4544</v>
+      </c>
+      <c r="D76" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000011C0</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C77">
+        <f t="shared" si="5"/>
+        <v>4608</v>
+      </c>
+      <c r="D77" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001200</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C78">
+        <f t="shared" si="5"/>
+        <v>4672</v>
+      </c>
+      <c r="D78" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001240</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C79">
+        <f t="shared" si="5"/>
+        <v>4736</v>
+      </c>
+      <c r="D79" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001280</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C80">
+        <f t="shared" si="5"/>
+        <v>4800</v>
+      </c>
+      <c r="D80" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000012C0</v>
+      </c>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C81">
+        <f t="shared" si="5"/>
+        <v>4864</v>
+      </c>
+      <c r="D81" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C82">
+        <f t="shared" si="5"/>
+        <v>4928</v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001340</v>
+      </c>
+    </row>
+    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <f t="shared" si="5"/>
+        <v>4992</v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001380</v>
+      </c>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C84">
+        <f t="shared" si="5"/>
+        <v>5056</v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000013C0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C85">
+        <f t="shared" si="5"/>
+        <v>5120</v>
+      </c>
+      <c r="D85" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001400</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <f t="shared" si="5"/>
+        <v>5184</v>
+      </c>
+      <c r="D86" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001440</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C87">
+        <f t="shared" si="5"/>
+        <v>5248</v>
+      </c>
+      <c r="D87" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001480</v>
+      </c>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C88">
+        <f t="shared" si="5"/>
+        <v>5312</v>
+      </c>
+      <c r="D88" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000014C0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C89">
+        <f t="shared" si="5"/>
+        <v>5376</v>
+      </c>
+      <c r="D89" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001500</v>
+      </c>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C90">
+        <f t="shared" si="5"/>
+        <v>5440</v>
+      </c>
+      <c r="D90" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001540</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C91">
+        <f t="shared" si="5"/>
+        <v>5504</v>
+      </c>
+      <c r="D91" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001580</v>
+      </c>
+    </row>
+    <row r="92" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C92">
+        <f t="shared" si="5"/>
+        <v>5568</v>
+      </c>
+      <c r="D92" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000015C0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C93">
+        <f t="shared" si="5"/>
+        <v>5632</v>
+      </c>
+      <c r="D93" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001600</v>
+      </c>
+    </row>
+    <row r="94" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C94">
+        <f t="shared" si="5"/>
+        <v>5696</v>
+      </c>
+      <c r="D94" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001640</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C95">
+        <f t="shared" si="5"/>
+        <v>5760</v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001680</v>
+      </c>
+    </row>
+    <row r="96" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C96">
+        <f t="shared" si="5"/>
+        <v>5824</v>
+      </c>
+      <c r="D96" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000016C0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C97">
+        <f t="shared" si="5"/>
+        <v>5888</v>
+      </c>
+      <c r="D97" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001700</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C98">
+        <f t="shared" si="5"/>
+        <v>5952</v>
+      </c>
+      <c r="D98" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001740</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C99">
+        <f t="shared" si="5"/>
+        <v>6016</v>
+      </c>
+      <c r="D99" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001780</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C100">
+        <f t="shared" si="5"/>
+        <v>6080</v>
+      </c>
+      <c r="D100" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000017C0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C101">
+        <f t="shared" si="5"/>
+        <v>6144</v>
+      </c>
+      <c r="D101" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001800</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C102">
+        <f t="shared" si="5"/>
+        <v>6208</v>
+      </c>
+      <c r="D102" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001840</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C103">
+        <f t="shared" si="5"/>
+        <v>6272</v>
+      </c>
+      <c r="D103" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001880</v>
+      </c>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C104">
+        <f t="shared" ref="C104:C145" si="7">C103+64</f>
+        <v>6336</v>
+      </c>
+      <c r="D104" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000018C0</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C105">
+        <f t="shared" si="7"/>
+        <v>6400</v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001900</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C106">
+        <f t="shared" si="7"/>
+        <v>6464</v>
+      </c>
+      <c r="D106" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001940</v>
+      </c>
+    </row>
+    <row r="107" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C107">
+        <f t="shared" si="7"/>
+        <v>6528</v>
+      </c>
+      <c r="D107" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001980</v>
+      </c>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C108">
+        <f t="shared" si="7"/>
+        <v>6592</v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="6"/>
+        <v>0x000019C0</v>
+      </c>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C109">
+        <f t="shared" si="7"/>
+        <v>6656</v>
+      </c>
+      <c r="D109" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001A00</v>
+      </c>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C110">
+        <f t="shared" si="7"/>
+        <v>6720</v>
+      </c>
+      <c r="D110" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001A40</v>
+      </c>
+    </row>
+    <row r="111" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C111">
+        <f t="shared" si="7"/>
+        <v>6784</v>
+      </c>
+      <c r="D111" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001A80</v>
+      </c>
+    </row>
+    <row r="112" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C112">
+        <f t="shared" si="7"/>
+        <v>6848</v>
+      </c>
+      <c r="D112" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001AC0</v>
+      </c>
+    </row>
+    <row r="113" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C113">
+        <f t="shared" si="7"/>
+        <v>6912</v>
+      </c>
+      <c r="D113" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001B00</v>
+      </c>
+    </row>
+    <row r="114" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C114">
+        <f t="shared" si="7"/>
+        <v>6976</v>
+      </c>
+      <c r="D114" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001B40</v>
+      </c>
+    </row>
+    <row r="115" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C115">
+        <f t="shared" si="7"/>
+        <v>7040</v>
+      </c>
+      <c r="D115" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001B80</v>
+      </c>
+    </row>
+    <row r="116" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C116">
+        <f t="shared" si="7"/>
+        <v>7104</v>
+      </c>
+      <c r="D116" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001BC0</v>
+      </c>
+    </row>
+    <row r="117" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C117">
+        <f t="shared" si="7"/>
+        <v>7168</v>
+      </c>
+      <c r="D117" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001C00</v>
+      </c>
+    </row>
+    <row r="118" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C118">
+        <f t="shared" si="7"/>
+        <v>7232</v>
+      </c>
+      <c r="D118" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001C40</v>
+      </c>
+    </row>
+    <row r="119" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C119">
+        <f t="shared" si="7"/>
+        <v>7296</v>
+      </c>
+      <c r="D119" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001C80</v>
+      </c>
+    </row>
+    <row r="120" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C120">
+        <f t="shared" si="7"/>
+        <v>7360</v>
+      </c>
+      <c r="D120" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001CC0</v>
+      </c>
+    </row>
+    <row r="121" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C121">
+        <f t="shared" si="7"/>
+        <v>7424</v>
+      </c>
+      <c r="D121" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001D00</v>
+      </c>
+    </row>
+    <row r="122" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C122">
+        <f t="shared" si="7"/>
+        <v>7488</v>
+      </c>
+      <c r="D122" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001D40</v>
+      </c>
+    </row>
+    <row r="123" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C123">
+        <f t="shared" si="7"/>
+        <v>7552</v>
+      </c>
+      <c r="D123" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001D80</v>
+      </c>
+    </row>
+    <row r="124" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C124">
+        <f t="shared" si="7"/>
+        <v>7616</v>
+      </c>
+      <c r="D124" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001DC0</v>
+      </c>
+    </row>
+    <row r="125" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C125">
+        <f t="shared" si="7"/>
+        <v>7680</v>
+      </c>
+      <c r="D125" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001E00</v>
+      </c>
+    </row>
+    <row r="126" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C126">
+        <f t="shared" si="7"/>
+        <v>7744</v>
+      </c>
+      <c r="D126" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001E40</v>
+      </c>
+    </row>
+    <row r="127" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C127">
+        <f t="shared" si="7"/>
+        <v>7808</v>
+      </c>
+      <c r="D127" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001E80</v>
+      </c>
+    </row>
+    <row r="128" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C128">
+        <f t="shared" si="7"/>
+        <v>7872</v>
+      </c>
+      <c r="D128" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001EC0</v>
+      </c>
+    </row>
+    <row r="129" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C129">
+        <f t="shared" si="7"/>
+        <v>7936</v>
+      </c>
+      <c r="D129" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001F00</v>
+      </c>
+    </row>
+    <row r="130" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C130">
+        <f t="shared" si="7"/>
+        <v>8000</v>
+      </c>
+      <c r="D130" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001F40</v>
+      </c>
+    </row>
+    <row r="131" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C131">
+        <f t="shared" si="7"/>
+        <v>8064</v>
+      </c>
+      <c r="D131" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001F80</v>
+      </c>
+    </row>
+    <row r="132" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C132">
+        <f t="shared" si="7"/>
+        <v>8128</v>
+      </c>
+      <c r="D132" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00001FC0</v>
+      </c>
+    </row>
+    <row r="133" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C133">
+        <f t="shared" si="7"/>
+        <v>8192</v>
+      </c>
+      <c r="D133" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00002000</v>
+      </c>
+    </row>
+    <row r="134" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C134">
+        <f t="shared" si="7"/>
+        <v>8256</v>
+      </c>
+      <c r="D134" t="str">
+        <f t="shared" si="6"/>
+        <v>0x00002040</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B1E6EA-2DB9-4BF4-B5ED-2EA9E3A35C2F}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF970AF-0373-4712-9F3B-6CF57294038B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/RS_D620/documents/RS_620_scratchpad.xlsx
+++ b/RS_D620/documents/RS_620_scratchpad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\POC\RS_D620\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688CB31C-557B-413D-8A4E-669739910684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FEAC6D-17D3-4380-917A-A776D52CCED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{77793D01-6217-42E2-9AFC-8B7FA38831D5}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Pinning!$A$1:$AX$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Pinning!$A$1:$AX$177</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="998">
   <si>
     <t>MON1</t>
   </si>
@@ -3031,6 +3031,15 @@
   </si>
   <si>
     <t>IDx0</t>
+  </si>
+  <si>
+    <t>PMB</t>
+  </si>
+  <si>
+    <t>PM_SDA</t>
+  </si>
+  <si>
+    <t>PM_SCL</t>
   </si>
 </sst>
 </file>
@@ -4428,6 +4437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D375968B-F291-4B7B-82A2-C039BEBF5DA0}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AX177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4583,7 +4593,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="19"/>
@@ -4645,7 +4655,7 @@
       <c r="AW2" s="19"/>
       <c r="AX2" s="19"/>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -4707,7 +4717,7 @@
       <c r="AW3" s="19"/>
       <c r="AX3" s="19"/>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="19"/>
@@ -4769,7 +4779,7 @@
       <c r="AW4" s="19"/>
       <c r="AX4" s="19"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
       <c r="E5" s="19"/>
@@ -4831,7 +4841,7 @@
       <c r="AW5" s="19"/>
       <c r="AX5" s="19"/>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>DEC2HEX(B6,2)</f>
         <v>01</v>
@@ -4883,7 +4893,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" ref="A7:A34" si="0">DEC2HEX(B7,2)</f>
         <v>02</v>
@@ -4935,7 +4945,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>03</v>
@@ -4987,7 +4997,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>04</v>
@@ -5040,7 +5050,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>05</v>
@@ -5098,7 +5108,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>06</v>
@@ -5156,7 +5166,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>07</v>
@@ -5217,7 +5227,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>08</v>
@@ -5276,7 +5286,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>09</v>
@@ -5337,7 +5347,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>0A</v>
@@ -5377,7 +5387,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>0B</v>
@@ -5417,7 +5427,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>0C</v>
@@ -5461,7 +5471,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>0D</v>
@@ -5510,7 +5520,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5582,7 +5592,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -5654,7 +5664,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -5729,7 +5739,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -5799,7 +5809,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -5871,7 +5881,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -5943,7 +5953,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -6004,7 +6014,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -6062,7 +6072,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6145,7 +6155,7 @@
       <c r="AW27" s="6"/>
       <c r="AX27" s="6"/>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>2A</v>
@@ -6228,7 +6238,7 @@
       <c r="AW28" s="6"/>
       <c r="AX28" s="6"/>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>2B</v>
@@ -6315,7 +6325,7 @@
       <c r="AW29" s="6"/>
       <c r="AX29" s="6"/>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>2C</v>
@@ -6381,7 +6391,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>2D</v>
@@ -6448,7 +6458,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>2E</v>
@@ -6503,7 +6513,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>2F</v>
@@ -6558,7 +6568,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6610,7 +6620,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F35" s="18" t="s">
         <v>878</v>
       </c>
@@ -6640,7 +6650,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>443</v>
       </c>
@@ -6706,7 +6716,7 @@
       <c r="AW36" s="6"/>
       <c r="AX36" s="6"/>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" ref="A37:A38" si="1">DEC2HEX(B37,2)</f>
         <v>1C</v>
@@ -6778,7 +6788,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="1"/>
         <v>1B</v>
@@ -6850,7 +6860,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F39" s="18" t="s">
         <v>459</v>
       </c>
@@ -7082,7 +7092,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="E42" s="7" t="s">
         <v>977</v>
       </c>
@@ -7130,7 +7140,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F43" s="18" t="s">
         <v>490</v>
       </c>
@@ -7172,7 +7182,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F44" s="18" t="s">
         <v>496</v>
       </c>
@@ -7217,7 +7227,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F45" s="18" t="s">
         <v>501</v>
       </c>
@@ -7262,7 +7272,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F46" s="18" t="s">
         <v>505</v>
       </c>
@@ -7307,7 +7317,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F47" s="24" t="s">
         <v>115</v>
       </c>
@@ -7384,7 +7394,7 @@
       <c r="AW47" s="6"/>
       <c r="AX47" s="6"/>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F48" s="24" t="s">
         <v>112</v>
       </c>
@@ -7463,7 +7473,7 @@
       <c r="AW48" s="6"/>
       <c r="AX48" s="6"/>
     </row>
-    <row r="49" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>358</v>
       </c>
@@ -7537,7 +7547,7 @@
       <c r="AW49" s="6"/>
       <c r="AX49" s="6"/>
     </row>
-    <row r="50" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>358</v>
       </c>
@@ -7605,7 +7615,7 @@
       <c r="AW50" s="6"/>
       <c r="AX50" s="6"/>
     </row>
-    <row r="51" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F51" s="18" t="s">
         <v>128</v>
       </c>
@@ -7661,7 +7671,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="52" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C52" t="s">
         <v>358</v>
       </c>
@@ -7720,7 +7730,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="53" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="D53" t="s">
         <v>548</v>
       </c>
@@ -7762,7 +7772,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="54" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>358</v>
       </c>
@@ -7812,7 +7822,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="55" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>157</v>
       </c>
@@ -7871,7 +7881,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="56" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>358</v>
       </c>
@@ -7925,7 +7935,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="57" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>241</v>
       </c>
@@ -7976,7 +7986,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="58" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
         <v>241</v>
       </c>
@@ -8024,7 +8034,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="59" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
         <v>241</v>
       </c>
@@ -8072,7 +8082,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="60" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>241</v>
       </c>
@@ -8120,7 +8130,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="61" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F61" s="18" t="s">
         <v>602</v>
       </c>
@@ -8159,7 +8169,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="62" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F62" s="18" t="s">
         <v>608</v>
       </c>
@@ -8192,7 +8202,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="63" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F63" s="18" t="s">
         <v>611</v>
       </c>
@@ -8222,7 +8232,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="64" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F64" s="18" t="s">
         <v>615</v>
       </c>
@@ -8254,7 +8264,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="65" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F65" s="18" t="s">
         <v>617</v>
       </c>
@@ -8413,7 +8423,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="68" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F68" s="18" t="s">
         <v>119</v>
       </c>
@@ -8472,7 +8482,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="69" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F69" s="18" t="s">
         <v>155</v>
       </c>
@@ -8528,7 +8538,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="70" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F70" s="18" t="s">
         <v>158</v>
       </c>
@@ -8584,7 +8594,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="71" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>358</v>
       </c>
@@ -8629,7 +8639,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="72" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C72" t="s">
         <v>358</v>
       </c>
@@ -8934,7 +8944,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="77" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
         <v>241</v>
       </c>
@@ -8998,7 +9008,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="78" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
         <v>358</v>
       </c>
@@ -9051,7 +9061,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="79" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C79" t="s">
         <v>358</v>
       </c>
@@ -9232,7 +9242,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f t="shared" ref="A82:A90" si="3">DEC2HEX(B82,2)</f>
         <v>0E</v>
@@ -9298,7 +9308,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
         <f t="shared" si="3"/>
         <v>0F</v>
@@ -9369,7 +9379,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -9428,7 +9438,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -9482,7 +9492,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -9539,7 +9549,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="str">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -9604,7 +9614,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="str">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -9663,7 +9673,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="str">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -9705,7 +9715,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="str">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -9748,6 +9758,12 @@
       </c>
     </row>
     <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>996</v>
+      </c>
+      <c r="C91" t="s">
+        <v>995</v>
+      </c>
       <c r="E91" s="7" t="s">
         <v>731</v>
       </c>
@@ -9801,6 +9817,12 @@
       </c>
     </row>
     <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>997</v>
+      </c>
+      <c r="C92" t="s">
+        <v>995</v>
+      </c>
       <c r="E92" s="7" t="s">
         <v>737</v>
       </c>
@@ -9853,7 +9875,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F93" s="18" t="s">
         <v>744</v>
       </c>
@@ -9880,7 +9902,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C94" t="s">
         <v>241</v>
       </c>
@@ -9933,7 +9955,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
         <v>241</v>
       </c>
@@ -9980,7 +10002,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C96" t="s">
         <v>358</v>
       </c>
@@ -10027,7 +10049,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="97" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F97" s="18" t="s">
         <v>767</v>
       </c>
@@ -10059,7 +10081,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="98" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F98" s="18" t="s">
         <v>770</v>
       </c>
@@ -10091,7 +10113,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="99" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F99" s="18" t="s">
         <v>772</v>
       </c>
@@ -10123,7 +10145,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="100" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F100" s="18" t="s">
         <v>777</v>
       </c>
@@ -10149,7 +10171,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="101" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F101" s="18" t="s">
         <v>779</v>
       </c>
@@ -10172,7 +10194,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="102" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="E102" s="7" t="s">
         <v>975</v>
       </c>
@@ -10207,7 +10229,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="103" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F103" s="18" t="s">
         <v>785</v>
       </c>
@@ -10248,7 +10270,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="104" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F104" s="18" t="s">
         <v>790</v>
       </c>
@@ -10292,7 +10314,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="105" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F105" s="18" t="s">
         <v>796</v>
       </c>
@@ -10330,7 +10352,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="106" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F106" s="18" t="s">
         <v>799</v>
       </c>
@@ -10359,7 +10381,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="107" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C107" t="s">
         <v>358</v>
       </c>
@@ -10400,7 +10422,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="108" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C108" t="s">
         <v>358</v>
       </c>
@@ -10441,7 +10463,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="109" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="F109" s="18" t="s">
         <v>134</v>
       </c>
@@ -10478,7 +10500,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="110" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C110" t="s">
         <v>358</v>
       </c>
@@ -10526,7 +10548,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="111" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
         <v>358</v>
       </c>
@@ -10574,7 +10596,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="112" spans="3:43" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="C112" t="s">
         <v>358</v>
       </c>
@@ -10622,7 +10644,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="113" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="C113" t="s">
         <v>358</v>
       </c>
@@ -10670,7 +10692,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="114" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="C114" t="s">
         <v>358</v>
       </c>
@@ -10718,7 +10740,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="115" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="C115" t="s">
         <v>358</v>
       </c>
@@ -10769,7 +10791,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="116" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="F116" s="18" t="s">
         <v>135</v>
       </c>
@@ -10809,7 +10831,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="117" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="C117" t="s">
         <v>241</v>
       </c>
@@ -10858,7 +10880,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="118" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="F118" s="18" t="s">
         <v>154</v>
       </c>
@@ -10910,7 +10932,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="119" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="str">
         <f t="shared" ref="A119:A120" si="4">DEC2HEX(B119,2)</f>
         <v>17</v>
@@ -10954,7 +10976,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="120" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="str">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -10998,7 +11020,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="121" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="F121" s="18" t="s">
         <v>81</v>
       </c>
@@ -11028,7 +11050,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="122" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="F122" s="18" t="s">
         <v>93</v>
       </c>
@@ -11058,7 +11080,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="123" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="F123" s="18" t="s">
         <v>108</v>
       </c>
@@ -11086,7 +11108,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="124" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="F124" s="18" t="s">
         <v>851</v>
       </c>
@@ -11109,7 +11131,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="125" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="C125" t="s">
         <v>241</v>
       </c>
@@ -11143,7 +11165,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="126" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="F126" s="18" t="s">
         <v>854</v>
       </c>
@@ -11169,7 +11191,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="127" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="F127" s="18" t="s">
         <v>857</v>
       </c>
@@ -11195,7 +11217,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="128" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
       <c r="C128" t="s">
         <v>358</v>
       </c>
@@ -11238,7 +11260,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="129" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F129" s="18" t="s">
         <v>150</v>
       </c>
@@ -11266,7 +11288,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="130" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F130" s="18" t="s">
         <v>151</v>
       </c>
@@ -11294,7 +11316,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="131" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F131" s="18" t="s">
         <v>153</v>
       </c>
@@ -11322,7 +11344,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="132" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F132" s="18" t="s">
         <v>869</v>
       </c>
@@ -11345,7 +11367,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="133" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F133" s="18" t="s">
         <v>871</v>
       </c>
@@ -11371,7 +11393,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="134" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="C134" t="s">
         <v>672</v>
       </c>
@@ -11405,7 +11427,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="135" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F135" s="18" t="s">
         <v>126</v>
       </c>
@@ -11433,7 +11455,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="136" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F136" s="18" t="s">
         <v>121</v>
       </c>
@@ -11461,7 +11483,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="137" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F137" s="18" t="s">
         <v>882</v>
       </c>
@@ -11493,7 +11515,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="138" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F138" s="18" t="s">
         <v>887</v>
       </c>
@@ -11525,7 +11547,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="139" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F139" s="20" t="s">
         <v>891</v>
       </c>
@@ -11584,7 +11606,7 @@
       <c r="AW139" s="19"/>
       <c r="AX139" s="19"/>
     </row>
-    <row r="140" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F140" s="20" t="s">
         <v>894</v>
       </c>
@@ -11643,7 +11665,7 @@
       <c r="AW140" s="19"/>
       <c r="AX140" s="19"/>
     </row>
-    <row r="141" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F141" s="20" t="s">
         <v>896</v>
       </c>
@@ -11702,7 +11724,7 @@
       <c r="AW141" s="19"/>
       <c r="AX141" s="19"/>
     </row>
-    <row r="142" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F142" s="20" t="s">
         <v>899</v>
       </c>
@@ -11761,7 +11783,7 @@
       <c r="AW142" s="19"/>
       <c r="AX142" s="19"/>
     </row>
-    <row r="143" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F143" s="20" t="s">
         <v>902</v>
       </c>
@@ -11820,7 +11842,7 @@
       <c r="AW143" s="19"/>
       <c r="AX143" s="19"/>
     </row>
-    <row r="144" spans="3:50" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F144" s="20" t="s">
         <v>905</v>
       </c>
@@ -11879,7 +11901,7 @@
       <c r="AW144" s="19"/>
       <c r="AX144" s="19"/>
     </row>
-    <row r="145" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="145" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F145" s="20" t="s">
         <v>908</v>
       </c>
@@ -11938,7 +11960,7 @@
       <c r="AW145" s="19"/>
       <c r="AX145" s="19"/>
     </row>
-    <row r="146" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="146" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F146" s="20" t="s">
         <v>911</v>
       </c>
@@ -11997,7 +12019,7 @@
       <c r="AW146" s="19"/>
       <c r="AX146" s="19"/>
     </row>
-    <row r="147" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="147" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F147" s="20" t="s">
         <v>913</v>
       </c>
@@ -12056,7 +12078,7 @@
       <c r="AW147" s="19"/>
       <c r="AX147" s="19"/>
     </row>
-    <row r="148" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="148" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F148" s="20" t="s">
         <v>913</v>
       </c>
@@ -12115,7 +12137,7 @@
       <c r="AW148" s="19"/>
       <c r="AX148" s="19"/>
     </row>
-    <row r="149" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="149" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F149" s="20" t="s">
         <v>913</v>
       </c>
@@ -12174,7 +12196,7 @@
       <c r="AW149" s="19"/>
       <c r="AX149" s="19"/>
     </row>
-    <row r="150" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="150" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F150" s="20" t="s">
         <v>913</v>
       </c>
@@ -12233,7 +12255,7 @@
       <c r="AW150" s="19"/>
       <c r="AX150" s="19"/>
     </row>
-    <row r="151" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="151" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F151" s="20" t="s">
         <v>913</v>
       </c>
@@ -12292,7 +12314,7 @@
       <c r="AW151" s="19"/>
       <c r="AX151" s="19"/>
     </row>
-    <row r="152" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="152" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F152" s="20" t="s">
         <v>913</v>
       </c>
@@ -12351,7 +12373,7 @@
       <c r="AW152" s="19"/>
       <c r="AX152" s="19"/>
     </row>
-    <row r="153" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="153" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F153" s="20" t="s">
         <v>913</v>
       </c>
@@ -12410,7 +12432,7 @@
       <c r="AW153" s="19"/>
       <c r="AX153" s="19"/>
     </row>
-    <row r="154" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="154" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F154" s="20" t="s">
         <v>913</v>
       </c>
@@ -12469,7 +12491,7 @@
       <c r="AW154" s="19"/>
       <c r="AX154" s="19"/>
     </row>
-    <row r="155" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="155" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F155" s="20" t="s">
         <v>913</v>
       </c>
@@ -12528,7 +12550,7 @@
       <c r="AW155" s="19"/>
       <c r="AX155" s="19"/>
     </row>
-    <row r="156" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="156" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F156" s="20" t="s">
         <v>915</v>
       </c>
@@ -12587,7 +12609,7 @@
       <c r="AW156" s="19"/>
       <c r="AX156" s="19"/>
     </row>
-    <row r="157" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="157" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F157" s="20" t="s">
         <v>918</v>
       </c>
@@ -12646,7 +12668,7 @@
       <c r="AW157" s="19"/>
       <c r="AX157" s="19"/>
     </row>
-    <row r="158" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="158" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F158" s="20" t="s">
         <v>921</v>
       </c>
@@ -12705,7 +12727,7 @@
       <c r="AW158" s="19"/>
       <c r="AX158" s="19"/>
     </row>
-    <row r="159" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="159" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F159" s="20" t="s">
         <v>923</v>
       </c>
@@ -12764,7 +12786,7 @@
       <c r="AW159" s="19"/>
       <c r="AX159" s="19"/>
     </row>
-    <row r="160" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="160" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F160" s="20" t="s">
         <v>925</v>
       </c>
@@ -12823,7 +12845,7 @@
       <c r="AW160" s="19"/>
       <c r="AX160" s="19"/>
     </row>
-    <row r="161" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="161" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F161" s="20" t="s">
         <v>927</v>
       </c>
@@ -12882,7 +12904,7 @@
       <c r="AW161" s="19"/>
       <c r="AX161" s="19"/>
     </row>
-    <row r="162" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="162" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F162" s="20" t="s">
         <v>929</v>
       </c>
@@ -12941,7 +12963,7 @@
       <c r="AW162" s="19"/>
       <c r="AX162" s="19"/>
     </row>
-    <row r="163" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="163" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F163" s="20" t="s">
         <v>931</v>
       </c>
@@ -13000,7 +13022,7 @@
       <c r="AW163" s="19"/>
       <c r="AX163" s="19"/>
     </row>
-    <row r="164" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="164" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F164" s="20" t="s">
         <v>933</v>
       </c>
@@ -13059,7 +13081,7 @@
       <c r="AW164" s="19"/>
       <c r="AX164" s="19"/>
     </row>
-    <row r="165" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="165" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F165" s="20" t="s">
         <v>933</v>
       </c>
@@ -13118,7 +13140,7 @@
       <c r="AW165" s="19"/>
       <c r="AX165" s="19"/>
     </row>
-    <row r="166" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="166" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F166" s="20" t="s">
         <v>933</v>
       </c>
@@ -13177,7 +13199,7 @@
       <c r="AW166" s="19"/>
       <c r="AX166" s="19"/>
     </row>
-    <row r="167" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="167" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F167" s="20" t="s">
         <v>933</v>
       </c>
@@ -13236,7 +13258,7 @@
       <c r="AW167" s="19"/>
       <c r="AX167" s="19"/>
     </row>
-    <row r="168" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="168" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F168" s="20" t="s">
         <v>933</v>
       </c>
@@ -13295,7 +13317,7 @@
       <c r="AW168" s="19"/>
       <c r="AX168" s="19"/>
     </row>
-    <row r="169" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="169" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F169" s="20" t="s">
         <v>933</v>
       </c>
@@ -13354,7 +13376,7 @@
       <c r="AW169" s="19"/>
       <c r="AX169" s="19"/>
     </row>
-    <row r="170" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="170" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F170" s="20" t="s">
         <v>933</v>
       </c>
@@ -13413,7 +13435,7 @@
       <c r="AW170" s="19"/>
       <c r="AX170" s="19"/>
     </row>
-    <row r="171" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="171" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F171" s="20" t="s">
         <v>933</v>
       </c>
@@ -13472,7 +13494,7 @@
       <c r="AW171" s="19"/>
       <c r="AX171" s="19"/>
     </row>
-    <row r="172" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="172" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F172" s="20" t="s">
         <v>933</v>
       </c>
@@ -13531,7 +13553,7 @@
       <c r="AW172" s="19"/>
       <c r="AX172" s="19"/>
     </row>
-    <row r="173" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="173" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F173" s="20" t="s">
         <v>935</v>
       </c>
@@ -13590,7 +13612,7 @@
       <c r="AW173" s="19"/>
       <c r="AX173" s="19"/>
     </row>
-    <row r="174" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="174" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F174" s="20" t="s">
         <v>938</v>
       </c>
@@ -13649,7 +13671,7 @@
       <c r="AW174" s="19"/>
       <c r="AX174" s="19"/>
     </row>
-    <row r="175" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="175" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F175" s="20" t="s">
         <v>941</v>
       </c>
@@ -13708,7 +13730,7 @@
       <c r="AW175" s="19"/>
       <c r="AX175" s="19"/>
     </row>
-    <row r="176" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="176" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F176" s="20" t="s">
         <v>944</v>
       </c>
@@ -13767,7 +13789,7 @@
       <c r="AW176" s="19"/>
       <c r="AX176" s="19"/>
     </row>
-    <row r="177" spans="6:50" x14ac:dyDescent="0.25">
+    <row r="177" spans="6:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="F177" s="20" t="s">
         <v>946</v>
       </c>
@@ -13827,7 +13849,13 @@
       <c r="AX177" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX1" xr:uid="{D375968B-F291-4B7B-82A2-C039BEBF5DA0}"/>
+  <autoFilter ref="A1:AX177" xr:uid="{D375968B-F291-4B7B-82A2-C039BEBF5DA0}">
+    <filterColumn colId="17">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
